--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c0a60b3eb224a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1110112f418e446d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1110112f418e446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c141647c18d4e52"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c141647c18d4e52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5d670d5ef434d50"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5d670d5ef434d50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5aa82d39d47943a6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5aa82d39d47943a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ece4c76b122461c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ece4c76b122461c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd18f339f59824748"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd18f339f59824748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref3d7a5693c5461c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref3d7a5693c5461c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref7df0a851054704"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref7df0a851054704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd531b6694b1d4a68"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd531b6694b1d4a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8f773ab758b94a3f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8f773ab758b94a3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02847a2f15ca4cc3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02847a2f15ca4cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R139f12a3e00f445d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R139f12a3e00f445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd733697ad4a14e70"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd733697ad4a14e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b0aa4ea75e74f2a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b0aa4ea75e74f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re058b64a3d764dce"/>
   </x:sheets>
 </x:workbook>
 </file>
